--- a/SN.xlsx
+++ b/SN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/Stocks/Data/Stocks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111BF60F-D668-1248-A560-6967D46C6994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40D8CF1-9BF9-574D-BED9-D324C9076EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -1133,20 +1133,19 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
+      <sheetName val="1. List_AutomaticData"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="9">
           <cell r="C9">
-            <v>114.77</v>
+            <v>119.6</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1553,7 +1552,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$9</f>
-        <v>114.77</v>
+        <v>119.6</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -1576,7 +1575,7 @@
       </c>
       <c r="C9" s="109">
         <f>C3*'Statement Q'!J18</f>
-        <v>16199900.27</v>
+        <v>16881659.599999998</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
@@ -1594,7 +1593,7 @@
       </c>
       <c r="C11" s="109">
         <f>C9+Overview!C10</f>
-        <v>16299731.27</v>
+        <v>16981490.599999998</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -1603,7 +1602,7 @@
       </c>
       <c r="C13" s="89">
         <f>C3/'Statement Q'!N21</f>
-        <v>23.248659253123158</v>
+        <v>24.227059742733548</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
@@ -1612,7 +1611,7 @@
       </c>
       <c r="C14" s="89">
         <f>C3/('Statement Q'!N5/'Statement Q'!N19)</f>
-        <v>2.5481365971745165</v>
+        <v>2.6553728066748468</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">

--- a/SN.xlsx
+++ b/SN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40D8CF1-9BF9-574D-BED9-D324C9076EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCF77F8-34AC-3844-92F6-E0A4479D3687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="3" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -1133,19 +1133,20 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
-      <sheetName val="1. List_AutomaticData"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="9">
           <cell r="C9">
-            <v>119.6</v>
+            <v>114.23</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1551,8 +1552,8 @@
         <v>72</v>
       </c>
       <c r="C3" s="35">
-        <f>[1]Sheet1!$C$9</f>
-        <v>119.6</v>
+        <f ca="1">[1]Sheet1!$C$9</f>
+        <v>114.23</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -1574,8 +1575,8 @@
         <v>173</v>
       </c>
       <c r="C9" s="109">
-        <f>C3*'Statement Q'!J18</f>
-        <v>16881659.599999998</v>
+        <f ca="1">C3*'Statement Q'!J18</f>
+        <v>16123678.73</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
@@ -1592,8 +1593,8 @@
         <v>175</v>
       </c>
       <c r="C11" s="109">
-        <f>C9+Overview!C10</f>
-        <v>16981490.599999998</v>
+        <f ca="1">C9+Overview!C10</f>
+        <v>16223509.73</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -1601,8 +1602,8 @@
         <v>170</v>
       </c>
       <c r="C13" s="89">
-        <f>C3/'Statement Q'!N21</f>
-        <v>24.227059742733548</v>
+        <f ca="1">C3/'Statement Q'!N21</f>
+        <v>23.139272862980381</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
@@ -1610,8 +1611,8 @@
         <v>171</v>
       </c>
       <c r="C14" s="89">
-        <f>C3/('Statement Q'!N5/'Statement Q'!N19)</f>
-        <v>2.6553728066748468</v>
+        <f ca="1">C3/('Statement Q'!N5/'Statement Q'!N19)</f>
+        <v>2.5361474557396972</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">

--- a/SN.xlsx
+++ b/SN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCF77F8-34AC-3844-92F6-E0A4479D3687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DC03B6-843A-5347-ABAC-474744D2F8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="3" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -1143,7 +1143,7 @@
       <sheetData sheetId="0">
         <row r="9">
           <cell r="C9">
-            <v>114.23</v>
+            <v>115.49</v>
           </cell>
         </row>
       </sheetData>
@@ -1552,8 +1552,8 @@
         <v>72</v>
       </c>
       <c r="C3" s="35">
-        <f ca="1">[1]Sheet1!$C$9</f>
-        <v>114.23</v>
+        <f>[1]Sheet1!$C$9</f>
+        <v>115.49</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -1575,8 +1575,8 @@
         <v>173</v>
       </c>
       <c r="C9" s="109">
-        <f ca="1">C3*'Statement Q'!J18</f>
-        <v>16123678.73</v>
+        <f>C3*'Statement Q'!J18</f>
+        <v>16301528.989999998</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
@@ -1593,8 +1593,8 @@
         <v>175</v>
       </c>
       <c r="C11" s="109">
-        <f ca="1">C9+Overview!C10</f>
-        <v>16223509.73</v>
+        <f>C9+Overview!C10</f>
+        <v>16401359.989999998</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -1602,8 +1602,8 @@
         <v>170</v>
       </c>
       <c r="C13" s="89">
-        <f ca="1">C3/'Statement Q'!N21</f>
-        <v>23.139272862980381</v>
+        <f>C3/'Statement Q'!N21</f>
+        <v>23.394507773313524</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
@@ -1611,8 +1611,8 @@
         <v>171</v>
       </c>
       <c r="C14" s="89">
-        <f ca="1">C3/('Statement Q'!N5/'Statement Q'!N19)</f>
-        <v>2.5361474557396972</v>
+        <f>C3/('Statement Q'!N5/'Statement Q'!N19)</f>
+        <v>2.5641221190876093</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">

--- a/SN.xlsx
+++ b/SN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DC03B6-843A-5347-ABAC-474744D2F8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07DF385-98BA-8B4A-8367-B51B4293E66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -1143,7 +1143,7 @@
       <sheetData sheetId="0">
         <row r="9">
           <cell r="C9">
-            <v>115.49</v>
+            <v>114.715</v>
           </cell>
         </row>
       </sheetData>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$9</f>
-        <v>115.49</v>
+        <v>114.715</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C9" s="109">
         <f>C3*'Statement Q'!J18</f>
-        <v>16301528.989999998</v>
+        <v>16192136.965</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C11" s="109">
         <f>C9+Overview!C10</f>
-        <v>16401359.989999998</v>
+        <v>16291967.965</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="C13" s="89">
         <f>C3/'Statement Q'!N21</f>
-        <v>23.394507773313524</v>
+        <v>23.237518046719728</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C14" s="89">
         <f>C3/('Statement Q'!N5/'Statement Q'!N19)</f>
-        <v>2.5641221190876093</v>
+        <v>2.5469154809172663</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -8941,6 +8941,7 @@
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="1"/>
+      <c r="O135" s="1"/>
     </row>
     <row r="136" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C136" s="87"/>

--- a/SN.xlsx
+++ b/SN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07DF385-98BA-8B4A-8367-B51B4293E66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83AC567-A67D-FA47-8A36-8176B8E69C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -1143,7 +1143,7 @@
       <sheetData sheetId="0">
         <row r="9">
           <cell r="C9">
-            <v>114.715</v>
+            <v>107.94</v>
           </cell>
         </row>
       </sheetData>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C3" s="35">
         <f>[1]Sheet1!$C$9</f>
-        <v>114.715</v>
+        <v>107.94</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C9" s="109">
         <f>C3*'Statement Q'!J18</f>
-        <v>16192136.965</v>
+        <v>15235838.939999999</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C11" s="109">
         <f>C9+Overview!C10</f>
-        <v>16291967.965</v>
+        <v>15335669.939999999</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="C13" s="89">
         <f>C3/'Statement Q'!N21</f>
-        <v>23.237518046719728</v>
+        <v>21.865123985206182</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C14" s="89">
         <f>C3/('Statement Q'!N5/'Statement Q'!N19)</f>
-        <v>2.5469154809172663</v>
+        <v>2.3964961601378176</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
